--- a/M-Project/M-Project_CED60/Docs/TLC59581.xlsx
+++ b/M-Project/M-Project_CED60/Docs/TLC59581.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\M-Project\M-Project_ES1\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\M-Project\M-Project_CED60\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0966A303-8CC9-4CEB-BB14-9335592DDDB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA912766-F55A-422E-940B-DDC44B8203C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="4095" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="10515" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLC59581 define" sheetId="11" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1361" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="638">
   <si>
     <t>BC DATA</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2270,6 +2270,10 @@
   <si>
     <t>Command List</t>
   </si>
+  <si>
+    <t>a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -3819,20 +3823,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAD89190-C7C4-4E49-8A60-EDF1AF01CC1D}">
-  <dimension ref="B2:G48"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <dimension ref="A1:G48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.5625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="24.5625" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.4375" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.4375" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.4375" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.4375" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.9375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.58203125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="24.58203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.4140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.4140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.4140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.4140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.9140625" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B2" s="38" t="s">
         <v>635</v>
       </c>
@@ -3844,7 +3853,7 @@
       <c r="F2" s="38"/>
       <c r="G2" s="38"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B3" s="52" t="s">
         <v>569</v>
       </c>
@@ -3862,7 +3871,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="38" t="s">
         <v>572</v>
       </c>
@@ -3882,7 +3891,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B5" s="38" t="s">
         <v>573</v>
       </c>
@@ -3902,7 +3911,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B6" s="38" t="s">
         <v>574</v>
       </c>
@@ -3920,7 +3929,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B7" s="38" t="s">
         <v>575</v>
       </c>
@@ -3938,7 +3947,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B8" s="38" t="s">
         <v>576</v>
       </c>
@@ -3956,7 +3965,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B10" s="38" t="s">
         <v>595</v>
       </c>
@@ -3964,7 +3973,7 @@
       <c r="D10" s="38"/>
       <c r="E10" s="38"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B11" s="38" t="s">
         <v>597</v>
       </c>
@@ -3978,7 +3987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B12" s="38">
         <v>1</v>
       </c>
@@ -3986,13 +3995,14 @@
         <v>30</v>
       </c>
       <c r="D12" s="41">
-        <v>100.5</v>
+        <f>'LED Current'!T15*1000</f>
+        <v>100.55283757338553</v>
       </c>
       <c r="E12" s="9">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B13" s="38">
         <v>2</v>
       </c>
@@ -4001,13 +4011,13 @@
       </c>
       <c r="D13" s="41">
         <f>D12*2</f>
-        <v>201</v>
+        <v>201.10567514677106</v>
       </c>
       <c r="E13" s="9">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B14" s="38">
         <v>3</v>
       </c>
@@ -4016,13 +4026,13 @@
       </c>
       <c r="D14" s="41">
         <f>D12*3</f>
-        <v>301.5</v>
+        <v>301.65851272015658</v>
       </c>
       <c r="E14" s="9">
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B15" s="38">
         <v>4</v>
       </c>
@@ -4031,13 +4041,13 @@
       </c>
       <c r="D15" s="41">
         <f>D12*4</f>
-        <v>402</v>
+        <v>402.21135029354213</v>
       </c>
       <c r="E15" s="9">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B17" s="38" t="s">
         <v>600</v>
       </c>
@@ -4046,7 +4056,7 @@
       <c r="E17" s="38"/>
       <c r="F17" s="38"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B18" s="38"/>
       <c r="C18" s="38" t="s">
         <v>631</v>
@@ -4061,7 +4071,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B19" s="38" t="s">
         <v>601</v>
       </c>
@@ -4081,7 +4091,7 @@
         <v>1, 31, 61, 91</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B20" s="38" t="s">
         <v>602</v>
       </c>
@@ -4101,7 +4111,7 @@
         <v>2, 32, 62, 92</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="38" t="s">
         <v>603</v>
       </c>
@@ -4121,7 +4131,7 @@
         <v>3, 33, 63, 93</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B22" s="38" t="s">
         <v>604</v>
       </c>
@@ -4141,7 +4151,7 @@
         <v>4, 34, 64, 94</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B23" s="38" t="s">
         <v>605</v>
       </c>
@@ -4161,7 +4171,7 @@
         <v>5, 35, 65, 95</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B24" s="38" t="s">
         <v>606</v>
       </c>
@@ -4181,7 +4191,7 @@
         <v>6, 36, 66, 96</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B25" s="38" t="s">
         <v>607</v>
       </c>
@@ -4201,7 +4211,7 @@
         <v>7, 37, 67, 97</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B26" s="38" t="s">
         <v>608</v>
       </c>
@@ -4221,7 +4231,7 @@
         <v>8, 38, 68, 98</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B27" s="38" t="s">
         <v>609</v>
       </c>
@@ -4241,7 +4251,7 @@
         <v>9, 39, 69, 99</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B28" s="38" t="s">
         <v>610</v>
       </c>
@@ -4261,7 +4271,7 @@
         <v>10, 40, 70, 100</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B29" s="38" t="s">
         <v>611</v>
       </c>
@@ -4281,7 +4291,7 @@
         <v>11, 41, 71, 101</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B30" s="38" t="s">
         <v>612</v>
       </c>
@@ -4301,7 +4311,7 @@
         <v>12, 42, 72, 102</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B31" s="38" t="s">
         <v>613</v>
       </c>
@@ -4321,7 +4331,7 @@
         <v>13, 43, 73, 103</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B32" s="38" t="s">
         <v>614</v>
       </c>
@@ -4341,7 +4351,7 @@
         <v>14, 44, 74, 104</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B33" s="38" t="s">
         <v>615</v>
       </c>
@@ -4361,7 +4371,7 @@
         <v>15, 45, 75, 105</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B34" s="38" t="s">
         <v>616</v>
       </c>
@@ -4381,7 +4391,7 @@
         <v>16, 46, 76, 106</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B35" s="38" t="s">
         <v>617</v>
       </c>
@@ -4401,7 +4411,7 @@
         <v>17, 47, 77, 107</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B36" s="38" t="s">
         <v>618</v>
       </c>
@@ -4421,7 +4431,7 @@
         <v>18, 48, 78, 108</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B37" s="38" t="s">
         <v>619</v>
       </c>
@@ -4441,7 +4451,7 @@
         <v>19, 49, 79, 109</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B38" s="38" t="s">
         <v>620</v>
       </c>
@@ -4461,7 +4471,7 @@
         <v>20, 50, 80, 110</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B39" s="38" t="s">
         <v>621</v>
       </c>
@@ -4481,7 +4491,7 @@
         <v>21, 51, 81, 111</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B40" s="38" t="s">
         <v>622</v>
       </c>
@@ -4501,7 +4511,7 @@
         <v>22, 52, 82, 112</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B41" s="38" t="s">
         <v>623</v>
       </c>
@@ -4521,7 +4531,7 @@
         <v>23, 53, 83, 113</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B42" s="38" t="s">
         <v>624</v>
       </c>
@@ -4541,7 +4551,7 @@
         <v>24, 54, 84, 114</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B43" s="38" t="s">
         <v>625</v>
       </c>
@@ -4561,7 +4571,7 @@
         <v>25, 55, 85, 115</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B44" s="38" t="s">
         <v>626</v>
       </c>
@@ -4581,7 +4591,7 @@
         <v>26, 56, 86, 116</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B45" s="38" t="s">
         <v>627</v>
       </c>
@@ -4601,7 +4611,7 @@
         <v>27, 57, 87, 117</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B46" s="38" t="s">
         <v>628</v>
       </c>
@@ -4621,7 +4631,7 @@
         <v>28, 58, 88, 118</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B47" s="38" t="s">
         <v>629</v>
       </c>
@@ -4641,7 +4651,7 @@
         <v>29, 59, 89, 119</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B48" s="38" t="s">
         <v>630</v>
       </c>
@@ -4675,22 +4685,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF277D8C-DEC8-468C-A721-FB951ADB61AD}">
   <dimension ref="B2:J21"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.5625" style="39" customWidth="1"/>
-    <col min="2" max="2" width="27.6875" style="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.8125" style="39" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.4375" style="39" customWidth="1"/>
-    <col min="5" max="6" width="4.4375" style="39" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.4375" style="39" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5625" style="39" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.4375" style="39" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.4375" style="39" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.3125" style="39" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.58203125" style="39" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="39" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.4140625" style="39" customWidth="1"/>
+    <col min="5" max="6" width="4.4140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.4140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.58203125" style="39" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.4140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.4140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.33203125" style="39" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="39"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B2" s="39" t="s">
         <v>283</v>
       </c>
@@ -4707,7 +4717,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B3" s="39" t="s">
         <v>285</v>
       </c>
@@ -4724,7 +4734,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B5" s="39" t="s">
         <v>299</v>
       </c>
@@ -4735,7 +4745,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B6" s="39" t="s">
         <v>293</v>
       </c>
@@ -4746,7 +4756,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B7" s="39" t="s">
         <v>286</v>
       </c>
@@ -4757,7 +4767,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="39" t="s">
         <v>287</v>
       </c>
@@ -4768,7 +4778,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="39" t="s">
         <v>289</v>
       </c>
@@ -4779,7 +4789,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="39" t="s">
         <v>290</v>
       </c>
@@ -4790,7 +4800,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.6">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="47" t="s">
         <v>291</v>
       </c>
@@ -4802,7 +4812,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B14" s="48" t="s">
         <v>292</v>
       </c>
@@ -4814,7 +4824,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.6">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B15" s="49" t="s">
         <v>295</v>
       </c>
@@ -4826,7 +4836,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B16" s="49" t="s">
         <v>302</v>
       </c>
@@ -4840,7 +4850,7 @@
       <c r="I16" s="42"/>
       <c r="J16" s="43"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B18" s="39" t="s">
         <v>297</v>
       </c>
@@ -4852,7 +4862,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B19" s="39" t="s">
         <v>298</v>
       </c>
@@ -4864,7 +4874,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B20" s="39" t="s">
         <v>300</v>
       </c>
@@ -4876,7 +4886,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B21" s="39" t="s">
         <v>301</v>
       </c>
@@ -4898,42 +4908,42 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA6438F-4E10-40CD-B988-9C47A9325743}">
   <dimension ref="B3:AD45"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.5625" customWidth="1"/>
-    <col min="2" max="2" width="14.4375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.9375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.1875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.5625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5625" customWidth="1"/>
-    <col min="7" max="7" width="15.9375" style="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.9375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.1875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.4375" style="36" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.5625" customWidth="1"/>
-    <col min="12" max="12" width="19.8125" style="26" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.4375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.0625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.3125" style="36" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.5625" customWidth="1"/>
-    <col min="17" max="17" width="19.8125" style="26" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.4375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.0625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.3125" style="36" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.5625" customWidth="1"/>
-    <col min="22" max="22" width="19.8125" style="26" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.4375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.0625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="32.3125" style="36" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.5625" customWidth="1"/>
-    <col min="27" max="27" width="19.8125" style="26" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.4375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.0625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="32.3125" style="36" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.58203125" customWidth="1"/>
+    <col min="2" max="2" width="14.4140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.58203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.58203125" customWidth="1"/>
+    <col min="7" max="7" width="15.9140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.9140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.4140625" style="36" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.58203125" customWidth="1"/>
+    <col min="12" max="12" width="19.83203125" style="26" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.4140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.08203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.33203125" style="36" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.58203125" customWidth="1"/>
+    <col min="17" max="17" width="19.83203125" style="26" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.4140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.08203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.33203125" style="36" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.58203125" customWidth="1"/>
+    <col min="22" max="22" width="19.83203125" style="26" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.4140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.08203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="32.33203125" style="36" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.58203125" customWidth="1"/>
+    <col min="27" max="27" width="19.83203125" style="26" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.4140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.08203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="32.33203125" style="36" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="7:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="3" spans="7:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="H3" s="53" t="s">
         <v>336</v>
       </c>
@@ -4955,7 +4965,7 @@
       </c>
       <c r="AC3" s="53"/>
     </row>
-    <row r="4" spans="7:30" x14ac:dyDescent="0.6">
+    <row r="4" spans="7:30" x14ac:dyDescent="0.45">
       <c r="G4" s="35" t="s">
         <v>339</v>
       </c>
@@ -5017,7 +5027,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="5" spans="7:30" x14ac:dyDescent="0.6">
+    <row r="5" spans="7:30" x14ac:dyDescent="0.45">
       <c r="G5" s="35" t="s">
         <v>340</v>
       </c>
@@ -5079,7 +5089,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="6" spans="7:30" x14ac:dyDescent="0.6">
+    <row r="6" spans="7:30" x14ac:dyDescent="0.45">
       <c r="G6" s="35" t="s">
         <v>341</v>
       </c>
@@ -5141,7 +5151,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="7" spans="7:30" x14ac:dyDescent="0.6">
+    <row r="7" spans="7:30" x14ac:dyDescent="0.45">
       <c r="H7" s="30"/>
       <c r="I7" s="31" t="s">
         <v>331</v>
@@ -5198,7 +5208,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="8" spans="7:30" x14ac:dyDescent="0.6">
+    <row r="8" spans="7:30" x14ac:dyDescent="0.45">
       <c r="G8" s="26" t="s">
         <v>342</v>
       </c>
@@ -5260,7 +5270,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="9" spans="7:30" x14ac:dyDescent="0.6">
+    <row r="9" spans="7:30" x14ac:dyDescent="0.45">
       <c r="G9" s="35" t="s">
         <v>343</v>
       </c>
@@ -5322,7 +5332,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="10" spans="7:30" x14ac:dyDescent="0.6">
+    <row r="10" spans="7:30" x14ac:dyDescent="0.45">
       <c r="G10" s="26" t="s">
         <v>344</v>
       </c>
@@ -5384,7 +5394,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="11" spans="7:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="11" spans="7:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="H11" s="32"/>
       <c r="I11" s="33" t="s">
         <v>335</v>
@@ -5441,7 +5451,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="12" spans="7:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="12" spans="7:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L12" s="35" t="s">
         <v>445</v>
       </c>
@@ -5491,7 +5501,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="7:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="14" spans="7:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="H14" s="53" t="s">
         <v>337</v>
       </c>
@@ -5513,7 +5523,7 @@
       </c>
       <c r="AC14" s="53"/>
     </row>
-    <row r="15" spans="7:30" x14ac:dyDescent="0.6">
+    <row r="15" spans="7:30" x14ac:dyDescent="0.45">
       <c r="G15" s="35" t="s">
         <v>339</v>
       </c>
@@ -5575,7 +5585,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="16" spans="7:30" x14ac:dyDescent="0.6">
+    <row r="16" spans="7:30" x14ac:dyDescent="0.45">
       <c r="G16" s="35" t="s">
         <v>340</v>
       </c>
@@ -5637,7 +5647,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="17" spans="2:30" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:30" x14ac:dyDescent="0.45">
       <c r="G17" s="35" t="s">
         <v>341</v>
       </c>
@@ -5699,7 +5709,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="18" spans="2:30" x14ac:dyDescent="0.6">
+    <row r="18" spans="2:30" x14ac:dyDescent="0.45">
       <c r="H18" s="30"/>
       <c r="I18" s="31" t="s">
         <v>331</v>
@@ -5756,7 +5766,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="19" spans="2:30" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:30" x14ac:dyDescent="0.45">
       <c r="G19" s="26" t="s">
         <v>351</v>
       </c>
@@ -5818,7 +5828,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="20" spans="2:30" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:30" x14ac:dyDescent="0.45">
       <c r="G20" s="35" t="s">
         <v>343</v>
       </c>
@@ -5880,7 +5890,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="21" spans="2:30" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:30" x14ac:dyDescent="0.45">
       <c r="G21" s="26" t="s">
         <v>344</v>
       </c>
@@ -5942,7 +5952,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="22" spans="2:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="22" spans="2:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="H22" s="32"/>
       <c r="I22" s="33" t="s">
         <v>335</v>
@@ -5999,7 +6009,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="23" spans="2:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="23" spans="2:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L23" s="35" t="s">
         <v>445</v>
       </c>
@@ -6049,7 +6059,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="2:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="25" spans="2:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C25" s="34" t="s">
         <v>355</v>
       </c>
@@ -6075,7 +6085,7 @@
       </c>
       <c r="AC25" s="53"/>
     </row>
-    <row r="26" spans="2:30" x14ac:dyDescent="0.6">
+    <row r="26" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B26" s="35" t="s">
         <v>341</v>
       </c>
@@ -6149,7 +6159,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="27" spans="2:30" x14ac:dyDescent="0.6">
+    <row r="27" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B27" s="35" t="s">
         <v>345</v>
       </c>
@@ -6223,7 +6233,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="28" spans="2:30" x14ac:dyDescent="0.6">
+    <row r="28" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B28" s="26" t="s">
         <v>346</v>
       </c>
@@ -6297,7 +6307,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="29" spans="2:30" x14ac:dyDescent="0.6">
+    <row r="29" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B29" s="26"/>
       <c r="C29" s="30"/>
       <c r="D29" s="31" t="s">
@@ -6362,7 +6372,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="30" spans="2:30" x14ac:dyDescent="0.6">
+    <row r="30" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B30" s="26" t="s">
         <v>346</v>
       </c>
@@ -6434,7 +6444,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="31" spans="2:30" x14ac:dyDescent="0.6">
+    <row r="31" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B31" s="35" t="s">
         <v>343</v>
       </c>
@@ -6506,7 +6516,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="32" spans="2:30" x14ac:dyDescent="0.6">
+    <row r="32" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B32" s="26" t="s">
         <v>344</v>
       </c>
@@ -6578,7 +6588,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="33" spans="2:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="33" spans="2:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C33" s="32"/>
       <c r="D33" s="33" t="s">
         <v>335</v>
@@ -6640,7 +6650,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="34" spans="2:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="34" spans="2:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L34" s="35" t="s">
         <v>445</v>
       </c>
@@ -6690,7 +6700,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="2:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="36" spans="2:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B36" s="35" t="s">
         <v>343</v>
       </c>
@@ -6715,7 +6725,7 @@
       </c>
       <c r="AC36" s="53"/>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.6">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B37" s="35" t="s">
         <v>339</v>
       </c>
@@ -6780,7 +6790,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.6">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B38" s="35" t="s">
         <v>340</v>
       </c>
@@ -6845,7 +6855,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.6">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B39" s="35" t="s">
         <v>341</v>
       </c>
@@ -6910,7 +6920,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.6">
+    <row r="40" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B40" s="35" t="s">
         <v>341</v>
       </c>
@@ -6970,7 +6980,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.6">
+    <row r="41" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B41" s="35" t="s">
         <v>345</v>
       </c>
@@ -7035,7 +7045,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.6">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B42" s="35" t="s">
         <v>445</v>
       </c>
@@ -7100,7 +7110,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.6">
+    <row r="43" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B43" s="35" t="s">
         <v>446</v>
       </c>
@@ -7143,7 +7153,7 @@
       </c>
       <c r="AD43" s="37"/>
     </row>
-    <row r="44" spans="2:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="44" spans="2:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B44" s="35" t="s">
         <v>447</v>
       </c>
@@ -7181,7 +7191,7 @@
       </c>
       <c r="AD44" s="37"/>
     </row>
-    <row r="45" spans="2:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="45" spans="2:30" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B45" s="35" t="s">
         <v>448</v>
       </c>
@@ -7236,18 +7246,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="W25:X25"/>
-    <mergeCell ref="AB25:AC25"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="AB36:AC36"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="W3:X3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="W14:X14"/>
-    <mergeCell ref="AB14:AC14"/>
     <mergeCell ref="H36:I36"/>
     <mergeCell ref="M3:N3"/>
     <mergeCell ref="M14:N14"/>
@@ -7256,6 +7254,18 @@
     <mergeCell ref="H25:I25"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="H14:I14"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="AB14:AC14"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="AB25:AC25"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="AB36:AC36"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7266,20 +7276,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D07B1369-D3F6-40CC-B5C3-2E8BB397A5C4}">
   <dimension ref="B1:DV122"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="8.0625" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.58203125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="8.08203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="6" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="124" width="6" style="9" customWidth="1"/>
-    <col min="125" max="125" width="10.0625" style="9" bestFit="1" customWidth="1"/>
-    <col min="126" max="126" width="6.8125" style="9" customWidth="1"/>
+    <col min="125" max="125" width="10.08203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="126" max="126" width="6.83203125" style="9" customWidth="1"/>
     <col min="127" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:126" ht="17.25" thickBot="1" x14ac:dyDescent="0.65"/>
-    <row r="2" spans="2:126" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="1" spans="2:126" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="2" spans="2:126" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C2" s="17"/>
       <c r="D2" s="6" t="s">
         <v>158</v>
@@ -7642,7 +7652,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="3" spans="2:126" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:126" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="54" t="s">
         <v>318</v>
       </c>
@@ -8018,7 +8028,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="4" spans="2:126" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:126" x14ac:dyDescent="0.45">
       <c r="B4" s="55"/>
       <c r="C4" s="19" t="s">
         <v>51</v>
@@ -8512,7 +8522,7 @@
         <v>43200</v>
       </c>
     </row>
-    <row r="5" spans="2:126" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:126" x14ac:dyDescent="0.45">
       <c r="B5" s="55"/>
       <c r="C5" s="19" t="s">
         <v>52</v>
@@ -8999,7 +9009,7 @@
       </c>
       <c r="DT5" s="10"/>
     </row>
-    <row r="6" spans="2:126" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:126" x14ac:dyDescent="0.45">
       <c r="B6" s="55"/>
       <c r="C6" s="19" t="s">
         <v>53</v>
@@ -9486,7 +9496,7 @@
       </c>
       <c r="DT6" s="10"/>
     </row>
-    <row r="7" spans="2:126" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:126" x14ac:dyDescent="0.45">
       <c r="B7" s="55"/>
       <c r="C7" s="19" t="s">
         <v>54</v>
@@ -9973,7 +9983,7 @@
       </c>
       <c r="DT7" s="10"/>
     </row>
-    <row r="8" spans="2:126" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:126" x14ac:dyDescent="0.45">
       <c r="B8" s="55"/>
       <c r="C8" s="19" t="s">
         <v>55</v>
@@ -10460,7 +10470,7 @@
       </c>
       <c r="DT8" s="10"/>
     </row>
-    <row r="9" spans="2:126" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:126" x14ac:dyDescent="0.45">
       <c r="B9" s="55"/>
       <c r="C9" s="19" t="s">
         <v>56</v>
@@ -10947,7 +10957,7 @@
       </c>
       <c r="DT9" s="10"/>
     </row>
-    <row r="10" spans="2:126" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:126" x14ac:dyDescent="0.45">
       <c r="B10" s="55"/>
       <c r="C10" s="19" t="s">
         <v>57</v>
@@ -11434,7 +11444,7 @@
       </c>
       <c r="DT10" s="10"/>
     </row>
-    <row r="11" spans="2:126" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:126" x14ac:dyDescent="0.45">
       <c r="B11" s="55"/>
       <c r="C11" s="19" t="s">
         <v>58</v>
@@ -11921,7 +11931,7 @@
       </c>
       <c r="DT11" s="10"/>
     </row>
-    <row r="12" spans="2:126" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:126" x14ac:dyDescent="0.45">
       <c r="B12" s="55"/>
       <c r="C12" s="19" t="s">
         <v>59</v>
@@ -12408,7 +12418,7 @@
       </c>
       <c r="DT12" s="10"/>
     </row>
-    <row r="13" spans="2:126" x14ac:dyDescent="0.6">
+    <row r="13" spans="2:126" x14ac:dyDescent="0.45">
       <c r="B13" s="55"/>
       <c r="C13" s="19" t="s">
         <v>60</v>
@@ -12895,7 +12905,7 @@
       </c>
       <c r="DT13" s="10"/>
     </row>
-    <row r="14" spans="2:126" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:126" x14ac:dyDescent="0.45">
       <c r="B14" s="55"/>
       <c r="C14" s="19" t="s">
         <v>61</v>
@@ -13382,7 +13392,7 @@
       </c>
       <c r="DT14" s="10"/>
     </row>
-    <row r="15" spans="2:126" x14ac:dyDescent="0.6">
+    <row r="15" spans="2:126" x14ac:dyDescent="0.45">
       <c r="B15" s="55"/>
       <c r="C15" s="19" t="s">
         <v>62</v>
@@ -13869,7 +13879,7 @@
       </c>
       <c r="DT15" s="10"/>
     </row>
-    <row r="16" spans="2:126" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:126" x14ac:dyDescent="0.45">
       <c r="B16" s="55"/>
       <c r="C16" s="19" t="s">
         <v>63</v>
@@ -14356,7 +14366,7 @@
       </c>
       <c r="DT16" s="10"/>
     </row>
-    <row r="17" spans="2:124" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:124" x14ac:dyDescent="0.45">
       <c r="B17" s="55"/>
       <c r="C17" s="19" t="s">
         <v>64</v>
@@ -14843,7 +14853,7 @@
       </c>
       <c r="DT17" s="10"/>
     </row>
-    <row r="18" spans="2:124" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="18" spans="2:124" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="56"/>
       <c r="C18" s="20" t="s">
         <v>65</v>
@@ -15330,7 +15340,7 @@
       </c>
       <c r="DT18" s="10"/>
     </row>
-    <row r="19" spans="2:124" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:124" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="54" t="s">
         <v>319</v>
       </c>
@@ -15819,7 +15829,7 @@
       </c>
       <c r="DT19" s="10"/>
     </row>
-    <row r="20" spans="2:124" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:124" x14ac:dyDescent="0.45">
       <c r="B20" s="55"/>
       <c r="C20" s="19" t="s">
         <v>304</v>
@@ -16306,7 +16316,7 @@
       </c>
       <c r="DT20" s="10"/>
     </row>
-    <row r="21" spans="2:124" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:124" x14ac:dyDescent="0.45">
       <c r="B21" s="55"/>
       <c r="C21" s="19" t="s">
         <v>66</v>
@@ -16793,7 +16803,7 @@
       </c>
       <c r="DT21" s="10"/>
     </row>
-    <row r="22" spans="2:124" x14ac:dyDescent="0.6">
+    <row r="22" spans="2:124" x14ac:dyDescent="0.45">
       <c r="B22" s="55"/>
       <c r="C22" s="19" t="s">
         <v>67</v>
@@ -17280,7 +17290,7 @@
       </c>
       <c r="DT22" s="10"/>
     </row>
-    <row r="23" spans="2:124" x14ac:dyDescent="0.6">
+    <row r="23" spans="2:124" x14ac:dyDescent="0.45">
       <c r="B23" s="55"/>
       <c r="C23" s="19" t="s">
         <v>68</v>
@@ -17767,7 +17777,7 @@
       </c>
       <c r="DT23" s="10"/>
     </row>
-    <row r="24" spans="2:124" x14ac:dyDescent="0.6">
+    <row r="24" spans="2:124" x14ac:dyDescent="0.45">
       <c r="B24" s="55"/>
       <c r="C24" s="19" t="s">
         <v>69</v>
@@ -18254,7 +18264,7 @@
       </c>
       <c r="DT24" s="10"/>
     </row>
-    <row r="25" spans="2:124" x14ac:dyDescent="0.6">
+    <row r="25" spans="2:124" x14ac:dyDescent="0.45">
       <c r="B25" s="55"/>
       <c r="C25" s="19" t="s">
         <v>70</v>
@@ -18741,7 +18751,7 @@
       </c>
       <c r="DT25" s="10"/>
     </row>
-    <row r="26" spans="2:124" x14ac:dyDescent="0.6">
+    <row r="26" spans="2:124" x14ac:dyDescent="0.45">
       <c r="B26" s="55"/>
       <c r="C26" s="19" t="s">
         <v>71</v>
@@ -19228,7 +19238,7 @@
       </c>
       <c r="DT26" s="10"/>
     </row>
-    <row r="27" spans="2:124" x14ac:dyDescent="0.6">
+    <row r="27" spans="2:124" x14ac:dyDescent="0.45">
       <c r="B27" s="55"/>
       <c r="C27" s="19" t="s">
         <v>72</v>
@@ -19715,7 +19725,7 @@
       </c>
       <c r="DT27" s="10"/>
     </row>
-    <row r="28" spans="2:124" x14ac:dyDescent="0.6">
+    <row r="28" spans="2:124" x14ac:dyDescent="0.45">
       <c r="B28" s="55"/>
       <c r="C28" s="19" t="s">
         <v>73</v>
@@ -20202,7 +20212,7 @@
       </c>
       <c r="DT28" s="10"/>
     </row>
-    <row r="29" spans="2:124" x14ac:dyDescent="0.6">
+    <row r="29" spans="2:124" x14ac:dyDescent="0.45">
       <c r="B29" s="55"/>
       <c r="C29" s="19" t="s">
         <v>74</v>
@@ -20688,7 +20698,7 @@
         <v>3239</v>
       </c>
     </row>
-    <row r="30" spans="2:124" x14ac:dyDescent="0.6">
+    <row r="30" spans="2:124" x14ac:dyDescent="0.45">
       <c r="B30" s="55"/>
       <c r="C30" s="19" t="s">
         <v>75</v>
@@ -21174,7 +21184,7 @@
         <v>3359</v>
       </c>
     </row>
-    <row r="31" spans="2:124" x14ac:dyDescent="0.6">
+    <row r="31" spans="2:124" x14ac:dyDescent="0.45">
       <c r="B31" s="55"/>
       <c r="C31" s="19" t="s">
         <v>76</v>
@@ -21660,7 +21670,7 @@
         <v>3479</v>
       </c>
     </row>
-    <row r="32" spans="2:124" x14ac:dyDescent="0.6">
+    <row r="32" spans="2:124" x14ac:dyDescent="0.45">
       <c r="B32" s="55"/>
       <c r="C32" s="19" t="s">
         <v>77</v>
@@ -22146,7 +22156,7 @@
         <v>3599</v>
       </c>
     </row>
-    <row r="33" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="33" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B33" s="55"/>
       <c r="C33" s="19" t="s">
         <v>78</v>
@@ -22632,7 +22642,7 @@
         <v>3719</v>
       </c>
     </row>
-    <row r="34" spans="2:123" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="34" spans="2:123" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B34" s="56"/>
       <c r="C34" s="20" t="s">
         <v>79</v>
@@ -23118,7 +23128,7 @@
         <v>3839</v>
       </c>
     </row>
-    <row r="35" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="35" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B35" s="54" t="s">
         <v>320</v>
       </c>
@@ -23606,7 +23616,7 @@
         <v>3959</v>
       </c>
     </row>
-    <row r="36" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="36" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B36" s="55"/>
       <c r="C36" s="19" t="s">
         <v>306</v>
@@ -24092,7 +24102,7 @@
         <v>4079</v>
       </c>
     </row>
-    <row r="37" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="37" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B37" s="55"/>
       <c r="C37" s="19" t="s">
         <v>80</v>
@@ -24578,7 +24588,7 @@
         <v>4199</v>
       </c>
     </row>
-    <row r="38" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="38" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B38" s="55"/>
       <c r="C38" s="19" t="s">
         <v>81</v>
@@ -25064,7 +25074,7 @@
         <v>4319</v>
       </c>
     </row>
-    <row r="39" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="39" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B39" s="55"/>
       <c r="C39" s="19" t="s">
         <v>82</v>
@@ -25550,7 +25560,7 @@
         <v>4439</v>
       </c>
     </row>
-    <row r="40" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="40" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B40" s="55"/>
       <c r="C40" s="19" t="s">
         <v>83</v>
@@ -26036,7 +26046,7 @@
         <v>4559</v>
       </c>
     </row>
-    <row r="41" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="41" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B41" s="55"/>
       <c r="C41" s="19" t="s">
         <v>84</v>
@@ -26522,7 +26532,7 @@
         <v>4679</v>
       </c>
     </row>
-    <row r="42" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="42" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B42" s="55"/>
       <c r="C42" s="19" t="s">
         <v>85</v>
@@ -27008,7 +27018,7 @@
         <v>4799</v>
       </c>
     </row>
-    <row r="43" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="43" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B43" s="55"/>
       <c r="C43" s="19" t="s">
         <v>86</v>
@@ -27494,7 +27504,7 @@
         <v>4919</v>
       </c>
     </row>
-    <row r="44" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="44" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B44" s="55"/>
       <c r="C44" s="19" t="s">
         <v>87</v>
@@ -27980,7 +27990,7 @@
         <v>5039</v>
       </c>
     </row>
-    <row r="45" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="45" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B45" s="55"/>
       <c r="C45" s="19" t="s">
         <v>88</v>
@@ -28466,7 +28476,7 @@
         <v>5159</v>
       </c>
     </row>
-    <row r="46" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="46" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B46" s="55"/>
       <c r="C46" s="19" t="s">
         <v>89</v>
@@ -28952,7 +28962,7 @@
         <v>5279</v>
       </c>
     </row>
-    <row r="47" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="47" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B47" s="55"/>
       <c r="C47" s="19" t="s">
         <v>90</v>
@@ -29438,7 +29448,7 @@
         <v>5399</v>
       </c>
     </row>
-    <row r="48" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="48" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B48" s="55"/>
       <c r="C48" s="19" t="s">
         <v>91</v>
@@ -29924,7 +29934,7 @@
         <v>5519</v>
       </c>
     </row>
-    <row r="49" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="49" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B49" s="55"/>
       <c r="C49" s="19" t="s">
         <v>92</v>
@@ -30410,7 +30420,7 @@
         <v>5639</v>
       </c>
     </row>
-    <row r="50" spans="2:123" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="50" spans="2:123" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B50" s="56"/>
       <c r="C50" s="20" t="s">
         <v>93</v>
@@ -30896,7 +30906,7 @@
         <v>5759</v>
       </c>
     </row>
-    <row r="51" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="51" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B51" s="54" t="s">
         <v>321</v>
       </c>
@@ -31384,7 +31394,7 @@
         <v>5879</v>
       </c>
     </row>
-    <row r="52" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="52" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B52" s="55"/>
       <c r="C52" s="19" t="s">
         <v>308</v>
@@ -31870,7 +31880,7 @@
         <v>5999</v>
       </c>
     </row>
-    <row r="53" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="53" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B53" s="55"/>
       <c r="C53" s="19" t="s">
         <v>94</v>
@@ -32356,7 +32366,7 @@
         <v>6119</v>
       </c>
     </row>
-    <row r="54" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="54" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B54" s="55"/>
       <c r="C54" s="19" t="s">
         <v>95</v>
@@ -32842,7 +32852,7 @@
         <v>6239</v>
       </c>
     </row>
-    <row r="55" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="55" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B55" s="55"/>
       <c r="C55" s="19" t="s">
         <v>96</v>
@@ -33328,7 +33338,7 @@
         <v>6359</v>
       </c>
     </row>
-    <row r="56" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="56" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B56" s="55"/>
       <c r="C56" s="19" t="s">
         <v>97</v>
@@ -33814,7 +33824,7 @@
         <v>6479</v>
       </c>
     </row>
-    <row r="57" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="57" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B57" s="55"/>
       <c r="C57" s="19" t="s">
         <v>98</v>
@@ -34300,7 +34310,7 @@
         <v>6599</v>
       </c>
     </row>
-    <row r="58" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="58" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B58" s="55"/>
       <c r="C58" s="19" t="s">
         <v>99</v>
@@ -34786,7 +34796,7 @@
         <v>6719</v>
       </c>
     </row>
-    <row r="59" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="59" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B59" s="55"/>
       <c r="C59" s="19" t="s">
         <v>100</v>
@@ -35272,7 +35282,7 @@
         <v>6839</v>
       </c>
     </row>
-    <row r="60" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="60" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B60" s="55"/>
       <c r="C60" s="19" t="s">
         <v>101</v>
@@ -35758,7 +35768,7 @@
         <v>6959</v>
       </c>
     </row>
-    <row r="61" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="61" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B61" s="55"/>
       <c r="C61" s="19" t="s">
         <v>102</v>
@@ -36244,7 +36254,7 @@
         <v>7079</v>
       </c>
     </row>
-    <row r="62" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="62" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B62" s="55"/>
       <c r="C62" s="19" t="s">
         <v>103</v>
@@ -36730,7 +36740,7 @@
         <v>7199</v>
       </c>
     </row>
-    <row r="63" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="63" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B63" s="55"/>
       <c r="C63" s="19" t="s">
         <v>104</v>
@@ -37216,7 +37226,7 @@
         <v>7319</v>
       </c>
     </row>
-    <row r="64" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="64" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B64" s="55"/>
       <c r="C64" s="19" t="s">
         <v>105</v>
@@ -37702,7 +37712,7 @@
         <v>7439</v>
       </c>
     </row>
-    <row r="65" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="65" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B65" s="55"/>
       <c r="C65" s="19" t="s">
         <v>106</v>
@@ -38188,7 +38198,7 @@
         <v>7559</v>
       </c>
     </row>
-    <row r="66" spans="2:123" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="66" spans="2:123" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B66" s="56"/>
       <c r="C66" s="20" t="s">
         <v>107</v>
@@ -38674,7 +38684,7 @@
         <v>7679</v>
       </c>
     </row>
-    <row r="67" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="67" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B67" s="54" t="s">
         <v>322</v>
       </c>
@@ -39162,7 +39172,7 @@
         <v>7799</v>
       </c>
     </row>
-    <row r="68" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="68" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B68" s="55"/>
       <c r="C68" s="19" t="s">
         <v>310</v>
@@ -39648,7 +39658,7 @@
         <v>7919</v>
       </c>
     </row>
-    <row r="69" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="69" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B69" s="55"/>
       <c r="C69" s="19" t="s">
         <v>108</v>
@@ -40134,7 +40144,7 @@
         <v>8039</v>
       </c>
     </row>
-    <row r="70" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="70" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B70" s="55"/>
       <c r="C70" s="19" t="s">
         <v>109</v>
@@ -40620,7 +40630,7 @@
         <v>8159</v>
       </c>
     </row>
-    <row r="71" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="71" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B71" s="55"/>
       <c r="C71" s="19" t="s">
         <v>110</v>
@@ -41106,7 +41116,7 @@
         <v>8279</v>
       </c>
     </row>
-    <row r="72" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="72" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B72" s="55"/>
       <c r="C72" s="19" t="s">
         <v>111</v>
@@ -41592,7 +41602,7 @@
         <v>8399</v>
       </c>
     </row>
-    <row r="73" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="73" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B73" s="55"/>
       <c r="C73" s="19" t="s">
         <v>112</v>
@@ -42078,7 +42088,7 @@
         <v>8519</v>
       </c>
     </row>
-    <row r="74" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="74" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B74" s="55"/>
       <c r="C74" s="19" t="s">
         <v>113</v>
@@ -42564,7 +42574,7 @@
         <v>8639</v>
       </c>
     </row>
-    <row r="75" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="75" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B75" s="55"/>
       <c r="C75" s="19" t="s">
         <v>114</v>
@@ -43050,7 +43060,7 @@
         <v>8759</v>
       </c>
     </row>
-    <row r="76" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="76" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B76" s="55"/>
       <c r="C76" s="19" t="s">
         <v>115</v>
@@ -43536,7 +43546,7 @@
         <v>8879</v>
       </c>
     </row>
-    <row r="77" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="77" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B77" s="55"/>
       <c r="C77" s="19" t="s">
         <v>116</v>
@@ -44022,7 +44032,7 @@
         <v>8999</v>
       </c>
     </row>
-    <row r="78" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="78" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B78" s="55"/>
       <c r="C78" s="19" t="s">
         <v>117</v>
@@ -44508,7 +44518,7 @@
         <v>9119</v>
       </c>
     </row>
-    <row r="79" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="79" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B79" s="55"/>
       <c r="C79" s="19" t="s">
         <v>118</v>
@@ -44994,7 +45004,7 @@
         <v>9239</v>
       </c>
     </row>
-    <row r="80" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="80" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B80" s="55"/>
       <c r="C80" s="19" t="s">
         <v>119</v>
@@ -45480,7 +45490,7 @@
         <v>9359</v>
       </c>
     </row>
-    <row r="81" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="81" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B81" s="55"/>
       <c r="C81" s="19" t="s">
         <v>120</v>
@@ -45966,7 +45976,7 @@
         <v>9479</v>
       </c>
     </row>
-    <row r="82" spans="2:123" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="82" spans="2:123" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B82" s="56"/>
       <c r="C82" s="20" t="s">
         <v>121</v>
@@ -46452,7 +46462,7 @@
         <v>9599</v>
       </c>
     </row>
-    <row r="83" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="83" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B83" s="54" t="s">
         <v>323</v>
       </c>
@@ -46940,7 +46950,7 @@
         <v>9719</v>
       </c>
     </row>
-    <row r="84" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="84" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B84" s="55"/>
       <c r="C84" s="19" t="s">
         <v>312</v>
@@ -47426,7 +47436,7 @@
         <v>9839</v>
       </c>
     </row>
-    <row r="85" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="85" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B85" s="55"/>
       <c r="C85" s="19" t="s">
         <v>122</v>
@@ -47912,7 +47922,7 @@
         <v>9959</v>
       </c>
     </row>
-    <row r="86" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="86" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B86" s="55"/>
       <c r="C86" s="19" t="s">
         <v>123</v>
@@ -48398,7 +48408,7 @@
         <v>10079</v>
       </c>
     </row>
-    <row r="87" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="87" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B87" s="55"/>
       <c r="C87" s="19" t="s">
         <v>124</v>
@@ -48884,7 +48894,7 @@
         <v>10199</v>
       </c>
     </row>
-    <row r="88" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="88" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B88" s="55"/>
       <c r="C88" s="19" t="s">
         <v>125</v>
@@ -49370,7 +49380,7 @@
         <v>10319</v>
       </c>
     </row>
-    <row r="89" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="89" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B89" s="55"/>
       <c r="C89" s="19" t="s">
         <v>126</v>
@@ -49856,7 +49866,7 @@
         <v>10439</v>
       </c>
     </row>
-    <row r="90" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="90" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B90" s="55"/>
       <c r="C90" s="19" t="s">
         <v>127</v>
@@ -50342,7 +50352,7 @@
         <v>10559</v>
       </c>
     </row>
-    <row r="91" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="91" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B91" s="55"/>
       <c r="C91" s="19" t="s">
         <v>128</v>
@@ -50828,7 +50838,7 @@
         <v>10679</v>
       </c>
     </row>
-    <row r="92" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="92" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B92" s="55"/>
       <c r="C92" s="19" t="s">
         <v>129</v>
@@ -51314,7 +51324,7 @@
         <v>10799</v>
       </c>
     </row>
-    <row r="93" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="93" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B93" s="55"/>
       <c r="C93" s="19" t="s">
         <v>130</v>
@@ -51800,7 +51810,7 @@
         <v>10919</v>
       </c>
     </row>
-    <row r="94" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="94" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B94" s="55"/>
       <c r="C94" s="19" t="s">
         <v>131</v>
@@ -52286,7 +52296,7 @@
         <v>11039</v>
       </c>
     </row>
-    <row r="95" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="95" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B95" s="55"/>
       <c r="C95" s="19" t="s">
         <v>132</v>
@@ -52772,7 +52782,7 @@
         <v>11159</v>
       </c>
     </row>
-    <row r="96" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="96" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B96" s="55"/>
       <c r="C96" s="19" t="s">
         <v>133</v>
@@ -53258,7 +53268,7 @@
         <v>11279</v>
       </c>
     </row>
-    <row r="97" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="97" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B97" s="55"/>
       <c r="C97" s="19" t="s">
         <v>134</v>
@@ -53744,7 +53754,7 @@
         <v>11399</v>
       </c>
     </row>
-    <row r="98" spans="2:123" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="98" spans="2:123" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B98" s="56"/>
       <c r="C98" s="20" t="s">
         <v>135</v>
@@ -54230,7 +54240,7 @@
         <v>11519</v>
       </c>
     </row>
-    <row r="99" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="99" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B99" s="54" t="s">
         <v>324</v>
       </c>
@@ -54718,7 +54728,7 @@
         <v>11639</v>
       </c>
     </row>
-    <row r="100" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="100" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B100" s="55"/>
       <c r="C100" s="19" t="s">
         <v>314</v>
@@ -55204,7 +55214,7 @@
         <v>11759</v>
       </c>
     </row>
-    <row r="101" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="101" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B101" s="55"/>
       <c r="C101" s="19" t="s">
         <v>136</v>
@@ -55690,7 +55700,7 @@
         <v>11879</v>
       </c>
     </row>
-    <row r="102" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="102" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B102" s="55"/>
       <c r="C102" s="19" t="s">
         <v>137</v>
@@ -56176,7 +56186,7 @@
         <v>11999</v>
       </c>
     </row>
-    <row r="103" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="103" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B103" s="55"/>
       <c r="C103" s="19" t="s">
         <v>138</v>
@@ -56662,7 +56672,7 @@
         <v>12119</v>
       </c>
     </row>
-    <row r="104" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="104" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B104" s="55"/>
       <c r="C104" s="19" t="s">
         <v>139</v>
@@ -57148,7 +57158,7 @@
         <v>12239</v>
       </c>
     </row>
-    <row r="105" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="105" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B105" s="55"/>
       <c r="C105" s="19" t="s">
         <v>140</v>
@@ -57634,7 +57644,7 @@
         <v>12359</v>
       </c>
     </row>
-    <row r="106" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="106" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B106" s="55"/>
       <c r="C106" s="19" t="s">
         <v>141</v>
@@ -58120,7 +58130,7 @@
         <v>12479</v>
       </c>
     </row>
-    <row r="107" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="107" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B107" s="55"/>
       <c r="C107" s="19" t="s">
         <v>142</v>
@@ -58606,7 +58616,7 @@
         <v>12599</v>
       </c>
     </row>
-    <row r="108" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="108" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B108" s="55"/>
       <c r="C108" s="19" t="s">
         <v>143</v>
@@ -59092,7 +59102,7 @@
         <v>12719</v>
       </c>
     </row>
-    <row r="109" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="109" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B109" s="55"/>
       <c r="C109" s="19" t="s">
         <v>144</v>
@@ -59578,7 +59588,7 @@
         <v>12839</v>
       </c>
     </row>
-    <row r="110" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="110" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B110" s="55"/>
       <c r="C110" s="19" t="s">
         <v>145</v>
@@ -60064,7 +60074,7 @@
         <v>12959</v>
       </c>
     </row>
-    <row r="111" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="111" spans="2:123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B111" s="55"/>
       <c r="C111" s="19" t="s">
         <v>146</v>
@@ -60550,7 +60560,7 @@
         <v>13079</v>
       </c>
     </row>
-    <row r="112" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="112" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B112" s="55"/>
       <c r="C112" s="19" t="s">
         <v>147</v>
@@ -61036,7 +61046,7 @@
         <v>13199</v>
       </c>
     </row>
-    <row r="113" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="113" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B113" s="55"/>
       <c r="C113" s="19" t="s">
         <v>148</v>
@@ -61522,7 +61532,7 @@
         <v>13319</v>
       </c>
     </row>
-    <row r="114" spans="2:123" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="114" spans="2:123" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B114" s="56"/>
       <c r="C114" s="20" t="s">
         <v>149</v>
@@ -62008,7 +62018,7 @@
         <v>13439</v>
       </c>
     </row>
-    <row r="115" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="115" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B115" s="54" t="s">
         <v>317</v>
       </c>
@@ -62496,7 +62506,7 @@
         <v>13559</v>
       </c>
     </row>
-    <row r="116" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="116" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B116" s="55"/>
       <c r="C116" s="19" t="s">
         <v>316</v>
@@ -62982,7 +62992,7 @@
         <v>13679</v>
       </c>
     </row>
-    <row r="117" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="117" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B117" s="55"/>
       <c r="C117" s="19" t="s">
         <v>150</v>
@@ -63468,7 +63478,7 @@
         <v>13799</v>
       </c>
     </row>
-    <row r="118" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="118" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B118" s="55"/>
       <c r="C118" s="19" t="s">
         <v>151</v>
@@ -63954,7 +63964,7 @@
         <v>13919</v>
       </c>
     </row>
-    <row r="119" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="119" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B119" s="55"/>
       <c r="C119" s="19" t="s">
         <v>152</v>
@@ -64440,7 +64450,7 @@
         <v>14039</v>
       </c>
     </row>
-    <row r="120" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="120" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B120" s="55"/>
       <c r="C120" s="19" t="s">
         <v>153</v>
@@ -64926,7 +64936,7 @@
         <v>14159</v>
       </c>
     </row>
-    <row r="121" spans="2:123" x14ac:dyDescent="0.6">
+    <row r="121" spans="2:123" x14ac:dyDescent="0.45">
       <c r="B121" s="55"/>
       <c r="C121" s="19" t="s">
         <v>154</v>
@@ -65412,7 +65422,7 @@
         <v>14279</v>
       </c>
     </row>
-    <row r="122" spans="2:123" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="122" spans="2:123" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B122" s="56"/>
       <c r="C122" s="20" t="s">
         <v>155</v>
@@ -65917,20 +65927,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7332034-DF4E-4698-945F-C1717E633D33}">
   <dimension ref="B1:AJ122"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="8.0625" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.58203125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="8.08203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="6" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="34" width="6" style="9" customWidth="1"/>
-    <col min="35" max="35" width="10.0625" style="9" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="6.8125" style="9" customWidth="1"/>
+    <col min="35" max="35" width="10.08203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="6.83203125" style="9" customWidth="1"/>
     <col min="37" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:36" ht="17.25" thickBot="1" x14ac:dyDescent="0.65"/>
-    <row r="2" spans="2:36" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="1" spans="2:36" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="2" spans="2:36" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C2" s="17"/>
       <c r="D2" s="6" t="s">
         <v>158</v>
@@ -66023,7 +66033,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="3" spans="2:36" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:36" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="54" t="s">
         <v>318</v>
       </c>
@@ -66129,7 +66139,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="4" spans="2:36" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B4" s="55"/>
       <c r="C4" s="19" t="s">
         <v>51</v>
@@ -66263,7 +66273,7 @@
         <v>10800</v>
       </c>
     </row>
-    <row r="5" spans="2:36" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B5" s="55"/>
       <c r="C5" s="19" t="s">
         <v>52</v>
@@ -66390,7 +66400,7 @@
       </c>
       <c r="AH5" s="10"/>
     </row>
-    <row r="6" spans="2:36" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B6" s="55"/>
       <c r="C6" s="19" t="s">
         <v>53</v>
@@ -66517,7 +66527,7 @@
       </c>
       <c r="AH6" s="10"/>
     </row>
-    <row r="7" spans="2:36" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B7" s="55"/>
       <c r="C7" s="19" t="s">
         <v>54</v>
@@ -66644,7 +66654,7 @@
       </c>
       <c r="AH7" s="10"/>
     </row>
-    <row r="8" spans="2:36" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B8" s="55"/>
       <c r="C8" s="19" t="s">
         <v>55</v>
@@ -66771,7 +66781,7 @@
       </c>
       <c r="AH8" s="10"/>
     </row>
-    <row r="9" spans="2:36" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B9" s="55"/>
       <c r="C9" s="19" t="s">
         <v>56</v>
@@ -66898,7 +66908,7 @@
       </c>
       <c r="AH9" s="10"/>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B10" s="55"/>
       <c r="C10" s="19" t="s">
         <v>57</v>
@@ -67025,7 +67035,7 @@
       </c>
       <c r="AH10" s="10"/>
     </row>
-    <row r="11" spans="2:36" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B11" s="55"/>
       <c r="C11" s="19" t="s">
         <v>58</v>
@@ -67152,7 +67162,7 @@
       </c>
       <c r="AH11" s="10"/>
     </row>
-    <row r="12" spans="2:36" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B12" s="55"/>
       <c r="C12" s="19" t="s">
         <v>59</v>
@@ -67279,7 +67289,7 @@
       </c>
       <c r="AH12" s="10"/>
     </row>
-    <row r="13" spans="2:36" x14ac:dyDescent="0.6">
+    <row r="13" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B13" s="55"/>
       <c r="C13" s="19" t="s">
         <v>60</v>
@@ -67406,7 +67416,7 @@
       </c>
       <c r="AH13" s="10"/>
     </row>
-    <row r="14" spans="2:36" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B14" s="55"/>
       <c r="C14" s="19" t="s">
         <v>61</v>
@@ -67533,7 +67543,7 @@
       </c>
       <c r="AH14" s="10"/>
     </row>
-    <row r="15" spans="2:36" x14ac:dyDescent="0.6">
+    <row r="15" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B15" s="55"/>
       <c r="C15" s="19" t="s">
         <v>62</v>
@@ -67660,7 +67670,7 @@
       </c>
       <c r="AH15" s="10"/>
     </row>
-    <row r="16" spans="2:36" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B16" s="55"/>
       <c r="C16" s="19" t="s">
         <v>63</v>
@@ -67787,7 +67797,7 @@
       </c>
       <c r="AH16" s="10"/>
     </row>
-    <row r="17" spans="2:34" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:34" x14ac:dyDescent="0.45">
       <c r="B17" s="55"/>
       <c r="C17" s="19" t="s">
         <v>64</v>
@@ -67914,7 +67924,7 @@
       </c>
       <c r="AH17" s="10"/>
     </row>
-    <row r="18" spans="2:34" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="18" spans="2:34" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="56"/>
       <c r="C18" s="20" t="s">
         <v>65</v>
@@ -68041,7 +68051,7 @@
       </c>
       <c r="AH18" s="10"/>
     </row>
-    <row r="19" spans="2:34" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:34" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="54" t="s">
         <v>319</v>
       </c>
@@ -68170,7 +68180,7 @@
       </c>
       <c r="AH19" s="10"/>
     </row>
-    <row r="20" spans="2:34" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:34" x14ac:dyDescent="0.45">
       <c r="B20" s="55"/>
       <c r="C20" s="19" t="s">
         <v>304</v>
@@ -68297,7 +68307,7 @@
       </c>
       <c r="AH20" s="10"/>
     </row>
-    <row r="21" spans="2:34" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:34" x14ac:dyDescent="0.45">
       <c r="B21" s="55"/>
       <c r="C21" s="19" t="s">
         <v>66</v>
@@ -68424,7 +68434,7 @@
       </c>
       <c r="AH21" s="10"/>
     </row>
-    <row r="22" spans="2:34" x14ac:dyDescent="0.6">
+    <row r="22" spans="2:34" x14ac:dyDescent="0.45">
       <c r="B22" s="55"/>
       <c r="C22" s="19" t="s">
         <v>67</v>
@@ -68551,7 +68561,7 @@
       </c>
       <c r="AH22" s="10"/>
     </row>
-    <row r="23" spans="2:34" x14ac:dyDescent="0.6">
+    <row r="23" spans="2:34" x14ac:dyDescent="0.45">
       <c r="B23" s="55"/>
       <c r="C23" s="19" t="s">
         <v>68</v>
@@ -68678,7 +68688,7 @@
       </c>
       <c r="AH23" s="10"/>
     </row>
-    <row r="24" spans="2:34" x14ac:dyDescent="0.6">
+    <row r="24" spans="2:34" x14ac:dyDescent="0.45">
       <c r="B24" s="55"/>
       <c r="C24" s="19" t="s">
         <v>69</v>
@@ -68805,7 +68815,7 @@
       </c>
       <c r="AH24" s="10"/>
     </row>
-    <row r="25" spans="2:34" x14ac:dyDescent="0.6">
+    <row r="25" spans="2:34" x14ac:dyDescent="0.45">
       <c r="B25" s="55"/>
       <c r="C25" s="19" t="s">
         <v>70</v>
@@ -68932,7 +68942,7 @@
       </c>
       <c r="AH25" s="10"/>
     </row>
-    <row r="26" spans="2:34" x14ac:dyDescent="0.6">
+    <row r="26" spans="2:34" x14ac:dyDescent="0.45">
       <c r="B26" s="55"/>
       <c r="C26" s="19" t="s">
         <v>71</v>
@@ -69059,7 +69069,7 @@
       </c>
       <c r="AH26" s="10"/>
     </row>
-    <row r="27" spans="2:34" x14ac:dyDescent="0.6">
+    <row r="27" spans="2:34" x14ac:dyDescent="0.45">
       <c r="B27" s="55"/>
       <c r="C27" s="19" t="s">
         <v>72</v>
@@ -69186,7 +69196,7 @@
       </c>
       <c r="AH27" s="10"/>
     </row>
-    <row r="28" spans="2:34" x14ac:dyDescent="0.6">
+    <row r="28" spans="2:34" x14ac:dyDescent="0.45">
       <c r="B28" s="55"/>
       <c r="C28" s="19" t="s">
         <v>73</v>
@@ -69313,7 +69323,7 @@
       </c>
       <c r="AH28" s="10"/>
     </row>
-    <row r="29" spans="2:34" x14ac:dyDescent="0.6">
+    <row r="29" spans="2:34" x14ac:dyDescent="0.45">
       <c r="B29" s="55"/>
       <c r="C29" s="19" t="s">
         <v>74</v>
@@ -69439,7 +69449,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="30" spans="2:34" x14ac:dyDescent="0.6">
+    <row r="30" spans="2:34" x14ac:dyDescent="0.45">
       <c r="B30" s="55"/>
       <c r="C30" s="19" t="s">
         <v>75</v>
@@ -69565,7 +69575,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="31" spans="2:34" x14ac:dyDescent="0.6">
+    <row r="31" spans="2:34" x14ac:dyDescent="0.45">
       <c r="B31" s="55"/>
       <c r="C31" s="19" t="s">
         <v>76</v>
@@ -69691,7 +69701,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="32" spans="2:34" x14ac:dyDescent="0.6">
+    <row r="32" spans="2:34" x14ac:dyDescent="0.45">
       <c r="B32" s="55"/>
       <c r="C32" s="19" t="s">
         <v>77</v>
@@ -69817,7 +69827,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="33" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="33" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B33" s="55"/>
       <c r="C33" s="19" t="s">
         <v>78</v>
@@ -69943,7 +69953,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="34" spans="2:33" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="34" spans="2:33" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B34" s="56"/>
       <c r="C34" s="20" t="s">
         <v>79</v>
@@ -70069,7 +70079,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="35" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="35" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B35" s="54" t="s">
         <v>320</v>
       </c>
@@ -70197,7 +70207,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="36" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="36" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B36" s="55"/>
       <c r="C36" s="19" t="s">
         <v>306</v>
@@ -70323,7 +70333,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B37" s="55"/>
       <c r="C37" s="19" t="s">
         <v>80</v>
@@ -70449,7 +70459,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B38" s="55"/>
       <c r="C38" s="19" t="s">
         <v>81</v>
@@ -70575,7 +70585,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B39" s="55"/>
       <c r="C39" s="19" t="s">
         <v>82</v>
@@ -70701,7 +70711,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="40" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B40" s="55"/>
       <c r="C40" s="19" t="s">
         <v>83</v>
@@ -70827,7 +70837,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="41" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B41" s="55"/>
       <c r="C41" s="19" t="s">
         <v>84</v>
@@ -70953,7 +70963,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B42" s="55"/>
       <c r="C42" s="19" t="s">
         <v>85</v>
@@ -71079,7 +71089,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B43" s="55"/>
       <c r="C43" s="19" t="s">
         <v>86</v>
@@ -71205,7 +71215,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B44" s="55"/>
       <c r="C44" s="19" t="s">
         <v>87</v>
@@ -71331,7 +71341,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B45" s="55"/>
       <c r="C45" s="19" t="s">
         <v>88</v>
@@ -71457,7 +71467,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B46" s="55"/>
       <c r="C46" s="19" t="s">
         <v>89</v>
@@ -71583,7 +71593,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B47" s="55"/>
       <c r="C47" s="19" t="s">
         <v>90</v>
@@ -71709,7 +71719,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="48" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="48" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B48" s="55"/>
       <c r="C48" s="19" t="s">
         <v>91</v>
@@ -71835,7 +71845,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="49" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="49" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B49" s="55"/>
       <c r="C49" s="19" t="s">
         <v>92</v>
@@ -71961,7 +71971,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="50" spans="2:33" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="50" spans="2:33" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B50" s="56"/>
       <c r="C50" s="20" t="s">
         <v>93</v>
@@ -72087,7 +72097,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="51" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="51" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B51" s="54" t="s">
         <v>321</v>
       </c>
@@ -72215,7 +72225,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="52" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="52" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B52" s="55"/>
       <c r="C52" s="19" t="s">
         <v>308</v>
@@ -72341,7 +72351,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="53" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="53" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B53" s="55"/>
       <c r="C53" s="19" t="s">
         <v>94</v>
@@ -72467,7 +72477,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="54" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="54" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B54" s="55"/>
       <c r="C54" s="19" t="s">
         <v>95</v>
@@ -72593,7 +72603,7 @@
         <v>1559</v>
       </c>
     </row>
-    <row r="55" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="55" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B55" s="55"/>
       <c r="C55" s="19" t="s">
         <v>96</v>
@@ -72719,7 +72729,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="56" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="56" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B56" s="55"/>
       <c r="C56" s="19" t="s">
         <v>97</v>
@@ -72845,7 +72855,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="57" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="57" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B57" s="55"/>
       <c r="C57" s="19" t="s">
         <v>98</v>
@@ -72971,7 +72981,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="58" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="58" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B58" s="55"/>
       <c r="C58" s="19" t="s">
         <v>99</v>
@@ -73097,7 +73107,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="59" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="59" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B59" s="55"/>
       <c r="C59" s="19" t="s">
         <v>100</v>
@@ -73223,7 +73233,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="60" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="60" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B60" s="55"/>
       <c r="C60" s="19" t="s">
         <v>101</v>
@@ -73349,7 +73359,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="61" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="61" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B61" s="55"/>
       <c r="C61" s="19" t="s">
         <v>102</v>
@@ -73475,7 +73485,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="62" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="62" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B62" s="55"/>
       <c r="C62" s="19" t="s">
         <v>103</v>
@@ -73601,7 +73611,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="63" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="63" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B63" s="55"/>
       <c r="C63" s="19" t="s">
         <v>104</v>
@@ -73727,7 +73737,7 @@
         <v>1829</v>
       </c>
     </row>
-    <row r="64" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="64" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B64" s="55"/>
       <c r="C64" s="19" t="s">
         <v>105</v>
@@ -73853,7 +73863,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="65" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B65" s="55"/>
       <c r="C65" s="19" t="s">
         <v>106</v>
@@ -73979,7 +73989,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="66" spans="2:33" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="66" spans="2:33" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B66" s="56"/>
       <c r="C66" s="20" t="s">
         <v>107</v>
@@ -74105,7 +74115,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="67" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="67" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B67" s="55" t="s">
         <v>322</v>
       </c>
@@ -74233,7 +74243,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="68" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B68" s="55"/>
       <c r="C68" s="19" t="s">
         <v>310</v>
@@ -74359,7 +74369,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="69" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B69" s="55"/>
       <c r="C69" s="19" t="s">
         <v>108</v>
@@ -74485,7 +74495,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="70" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B70" s="55"/>
       <c r="C70" s="19" t="s">
         <v>109</v>
@@ -74611,7 +74621,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="71" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B71" s="55"/>
       <c r="C71" s="19" t="s">
         <v>110</v>
@@ -74737,7 +74747,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="72" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B72" s="55"/>
       <c r="C72" s="19" t="s">
         <v>111</v>
@@ -74863,7 +74873,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B73" s="55"/>
       <c r="C73" s="19" t="s">
         <v>112</v>
@@ -74989,7 +74999,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="74" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B74" s="55"/>
       <c r="C74" s="19" t="s">
         <v>113</v>
@@ -75115,7 +75125,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="75" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B75" s="55"/>
       <c r="C75" s="19" t="s">
         <v>114</v>
@@ -75241,7 +75251,7 @@
         <v>2189</v>
       </c>
     </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="76" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B76" s="55"/>
       <c r="C76" s="19" t="s">
         <v>115</v>
@@ -75367,7 +75377,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B77" s="55"/>
       <c r="C77" s="19" t="s">
         <v>116</v>
@@ -75493,7 +75503,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="78" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="78" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B78" s="55"/>
       <c r="C78" s="19" t="s">
         <v>117</v>
@@ -75619,7 +75629,7 @@
         <v>2279</v>
       </c>
     </row>
-    <row r="79" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="79" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B79" s="55"/>
       <c r="C79" s="19" t="s">
         <v>118</v>
@@ -75745,7 +75755,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B80" s="55"/>
       <c r="C80" s="19" t="s">
         <v>119</v>
@@ -75871,7 +75881,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="81" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="81" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B81" s="55"/>
       <c r="C81" s="19" t="s">
         <v>120</v>
@@ -75997,7 +76007,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="82" spans="2:33" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="82" spans="2:33" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B82" s="55"/>
       <c r="C82" s="19" t="s">
         <v>121</v>
@@ -76123,7 +76133,7 @@
         <v>2399</v>
       </c>
     </row>
-    <row r="83" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="83" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B83" s="54" t="s">
         <v>323</v>
       </c>
@@ -76251,7 +76261,7 @@
         <v>2429</v>
       </c>
     </row>
-    <row r="84" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="84" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B84" s="55"/>
       <c r="C84" s="19" t="s">
         <v>312</v>
@@ -76377,7 +76387,7 @@
         <v>2459</v>
       </c>
     </row>
-    <row r="85" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="85" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B85" s="55"/>
       <c r="C85" s="19" t="s">
         <v>122</v>
@@ -76503,7 +76513,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="86" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="86" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B86" s="55"/>
       <c r="C86" s="19" t="s">
         <v>123</v>
@@ -76629,7 +76639,7 @@
         <v>2519</v>
       </c>
     </row>
-    <row r="87" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="87" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B87" s="55"/>
       <c r="C87" s="19" t="s">
         <v>124</v>
@@ -76755,7 +76765,7 @@
         <v>2549</v>
       </c>
     </row>
-    <row r="88" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="88" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B88" s="55"/>
       <c r="C88" s="19" t="s">
         <v>125</v>
@@ -76881,7 +76891,7 @@
         <v>2579</v>
       </c>
     </row>
-    <row r="89" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="89" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B89" s="55"/>
       <c r="C89" s="19" t="s">
         <v>126</v>
@@ -77007,7 +77017,7 @@
         <v>2609</v>
       </c>
     </row>
-    <row r="90" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="90" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B90" s="55"/>
       <c r="C90" s="19" t="s">
         <v>127</v>
@@ -77133,7 +77143,7 @@
         <v>2639</v>
       </c>
     </row>
-    <row r="91" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="91" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B91" s="55"/>
       <c r="C91" s="19" t="s">
         <v>128</v>
@@ -77259,7 +77269,7 @@
         <v>2669</v>
       </c>
     </row>
-    <row r="92" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="92" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B92" s="55"/>
       <c r="C92" s="19" t="s">
         <v>129</v>
@@ -77385,7 +77395,7 @@
         <v>2699</v>
       </c>
     </row>
-    <row r="93" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="93" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B93" s="55"/>
       <c r="C93" s="19" t="s">
         <v>130</v>
@@ -77511,7 +77521,7 @@
         <v>2729</v>
       </c>
     </row>
-    <row r="94" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="94" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B94" s="55"/>
       <c r="C94" s="19" t="s">
         <v>131</v>
@@ -77637,7 +77647,7 @@
         <v>2759</v>
       </c>
     </row>
-    <row r="95" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="95" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B95" s="55"/>
       <c r="C95" s="19" t="s">
         <v>132</v>
@@ -77763,7 +77773,7 @@
         <v>2789</v>
       </c>
     </row>
-    <row r="96" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="96" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B96" s="55"/>
       <c r="C96" s="19" t="s">
         <v>133</v>
@@ -77889,7 +77899,7 @@
         <v>2819</v>
       </c>
     </row>
-    <row r="97" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="97" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B97" s="55"/>
       <c r="C97" s="19" t="s">
         <v>134</v>
@@ -78015,7 +78025,7 @@
         <v>2849</v>
       </c>
     </row>
-    <row r="98" spans="2:33" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="98" spans="2:33" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B98" s="56"/>
       <c r="C98" s="20" t="s">
         <v>135</v>
@@ -78141,7 +78151,7 @@
         <v>2879</v>
       </c>
     </row>
-    <row r="99" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="99" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B99" s="55" t="s">
         <v>324</v>
       </c>
@@ -78269,7 +78279,7 @@
         <v>2909</v>
       </c>
     </row>
-    <row r="100" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="100" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B100" s="55"/>
       <c r="C100" s="19" t="s">
         <v>314</v>
@@ -78395,7 +78405,7 @@
         <v>2939</v>
       </c>
     </row>
-    <row r="101" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="101" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B101" s="55"/>
       <c r="C101" s="19" t="s">
         <v>136</v>
@@ -78521,7 +78531,7 @@
         <v>2969</v>
       </c>
     </row>
-    <row r="102" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="102" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B102" s="55"/>
       <c r="C102" s="19" t="s">
         <v>137</v>
@@ -78647,7 +78657,7 @@
         <v>2999</v>
       </c>
     </row>
-    <row r="103" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="103" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B103" s="55"/>
       <c r="C103" s="19" t="s">
         <v>138</v>
@@ -78773,7 +78783,7 @@
         <v>3029</v>
       </c>
     </row>
-    <row r="104" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="104" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B104" s="55"/>
       <c r="C104" s="19" t="s">
         <v>139</v>
@@ -78899,7 +78909,7 @@
         <v>3059</v>
       </c>
     </row>
-    <row r="105" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="105" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B105" s="55"/>
       <c r="C105" s="19" t="s">
         <v>140</v>
@@ -79025,7 +79035,7 @@
         <v>3089</v>
       </c>
     </row>
-    <row r="106" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="106" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B106" s="55"/>
       <c r="C106" s="19" t="s">
         <v>141</v>
@@ -79151,7 +79161,7 @@
         <v>3119</v>
       </c>
     </row>
-    <row r="107" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="107" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B107" s="55"/>
       <c r="C107" s="19" t="s">
         <v>142</v>
@@ -79277,7 +79287,7 @@
         <v>3149</v>
       </c>
     </row>
-    <row r="108" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="108" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B108" s="55"/>
       <c r="C108" s="19" t="s">
         <v>143</v>
@@ -79403,7 +79413,7 @@
         <v>3179</v>
       </c>
     </row>
-    <row r="109" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="109" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B109" s="55"/>
       <c r="C109" s="19" t="s">
         <v>144</v>
@@ -79529,7 +79539,7 @@
         <v>3209</v>
       </c>
     </row>
-    <row r="110" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="110" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B110" s="55"/>
       <c r="C110" s="19" t="s">
         <v>145</v>
@@ -79655,7 +79665,7 @@
         <v>3239</v>
       </c>
     </row>
-    <row r="111" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="111" spans="2:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B111" s="55"/>
       <c r="C111" s="19" t="s">
         <v>146</v>
@@ -79781,7 +79791,7 @@
         <v>3269</v>
       </c>
     </row>
-    <row r="112" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="112" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B112" s="55"/>
       <c r="C112" s="19" t="s">
         <v>147</v>
@@ -79907,7 +79917,7 @@
         <v>3299</v>
       </c>
     </row>
-    <row r="113" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="113" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B113" s="55"/>
       <c r="C113" s="19" t="s">
         <v>148</v>
@@ -80033,7 +80043,7 @@
         <v>3329</v>
       </c>
     </row>
-    <row r="114" spans="2:33" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="114" spans="2:33" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B114" s="55"/>
       <c r="C114" s="19" t="s">
         <v>149</v>
@@ -80159,7 +80169,7 @@
         <v>3359</v>
       </c>
     </row>
-    <row r="115" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="115" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B115" s="54" t="s">
         <v>317</v>
       </c>
@@ -80287,7 +80297,7 @@
         <v>3389</v>
       </c>
     </row>
-    <row r="116" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="116" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B116" s="55"/>
       <c r="C116" s="19" t="s">
         <v>316</v>
@@ -80413,7 +80423,7 @@
         <v>3419</v>
       </c>
     </row>
-    <row r="117" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="117" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B117" s="55"/>
       <c r="C117" s="19" t="s">
         <v>150</v>
@@ -80539,7 +80549,7 @@
         <v>3449</v>
       </c>
     </row>
-    <row r="118" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="118" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B118" s="55"/>
       <c r="C118" s="19" t="s">
         <v>151</v>
@@ -80665,7 +80675,7 @@
         <v>3479</v>
       </c>
     </row>
-    <row r="119" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="119" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B119" s="55"/>
       <c r="C119" s="19" t="s">
         <v>152</v>
@@ -80791,7 +80801,7 @@
         <v>3509</v>
       </c>
     </row>
-    <row r="120" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="120" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B120" s="55"/>
       <c r="C120" s="19" t="s">
         <v>153</v>
@@ -80917,7 +80927,7 @@
         <v>3539</v>
       </c>
     </row>
-    <row r="121" spans="2:33" x14ac:dyDescent="0.6">
+    <row r="121" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B121" s="55"/>
       <c r="C121" s="19" t="s">
         <v>154</v>
@@ -81043,7 +81053,7 @@
         <v>3569</v>
       </c>
     </row>
-    <row r="122" spans="2:33" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="122" spans="2:33" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B122" s="56"/>
       <c r="C122" s="20" t="s">
         <v>155</v>
@@ -81188,13 +81198,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="N2:T64"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.625" customWidth="1"/>
+    <col min="1" max="1" width="2.58203125" customWidth="1"/>
     <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="14:20" x14ac:dyDescent="0.6">
+    <row r="2" spans="14:20" x14ac:dyDescent="0.45">
       <c r="N2" t="s">
         <v>0</v>
       </c>
@@ -81217,7 +81227,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="14:20" x14ac:dyDescent="0.6">
+    <row r="3" spans="14:20" x14ac:dyDescent="0.45">
       <c r="N3">
         <v>0</v>
       </c>
@@ -81242,7 +81252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="14:20" x14ac:dyDescent="0.6">
+    <row r="4" spans="14:20" x14ac:dyDescent="0.45">
       <c r="S4">
         <v>1</v>
       </c>
@@ -81251,7 +81261,7 @@
         <v>4.0221135029354206E-3</v>
       </c>
     </row>
-    <row r="5" spans="14:20" x14ac:dyDescent="0.6">
+    <row r="5" spans="14:20" x14ac:dyDescent="0.45">
       <c r="S5">
         <v>2</v>
       </c>
@@ -81260,7 +81270,7 @@
         <v>8.0442270058708413E-3</v>
       </c>
     </row>
-    <row r="6" spans="14:20" x14ac:dyDescent="0.6">
+    <row r="6" spans="14:20" x14ac:dyDescent="0.45">
       <c r="S6">
         <v>3</v>
       </c>
@@ -81269,7 +81279,7 @@
         <v>1.2066340508806261E-2</v>
       </c>
     </row>
-    <row r="7" spans="14:20" x14ac:dyDescent="0.6">
+    <row r="7" spans="14:20" x14ac:dyDescent="0.45">
       <c r="S7">
         <v>4</v>
       </c>
@@ -81278,7 +81288,7 @@
         <v>1.6088454011741683E-2</v>
       </c>
     </row>
-    <row r="8" spans="14:20" x14ac:dyDescent="0.6">
+    <row r="8" spans="14:20" x14ac:dyDescent="0.45">
       <c r="S8">
         <v>5</v>
       </c>
@@ -81287,7 +81297,7 @@
         <v>2.0110567514677102E-2</v>
       </c>
     </row>
-    <row r="9" spans="14:20" x14ac:dyDescent="0.6">
+    <row r="9" spans="14:20" x14ac:dyDescent="0.45">
       <c r="S9">
         <v>6</v>
       </c>
@@ -81296,7 +81306,7 @@
         <v>2.4132681017612522E-2</v>
       </c>
     </row>
-    <row r="10" spans="14:20" x14ac:dyDescent="0.6">
+    <row r="10" spans="14:20" x14ac:dyDescent="0.45">
       <c r="S10">
         <v>7</v>
       </c>
@@ -81305,7 +81315,7 @@
         <v>2.8154794520547945E-2</v>
       </c>
     </row>
-    <row r="11" spans="14:20" x14ac:dyDescent="0.6">
+    <row r="11" spans="14:20" x14ac:dyDescent="0.45">
       <c r="S11">
         <v>8</v>
       </c>
@@ -81314,7 +81324,7 @@
         <v>3.2176908023483365E-2</v>
       </c>
     </row>
-    <row r="12" spans="14:20" x14ac:dyDescent="0.6">
+    <row r="12" spans="14:20" x14ac:dyDescent="0.45">
       <c r="S12">
         <v>9</v>
       </c>
@@ -81323,7 +81333,7 @@
         <v>3.6199021526418781E-2</v>
       </c>
     </row>
-    <row r="13" spans="14:20" x14ac:dyDescent="0.6">
+    <row r="13" spans="14:20" x14ac:dyDescent="0.45">
       <c r="S13">
         <v>10</v>
       </c>
@@ -81332,7 +81342,7 @@
         <v>4.0221135029354205E-2</v>
       </c>
     </row>
-    <row r="14" spans="14:20" x14ac:dyDescent="0.6">
+    <row r="14" spans="14:20" x14ac:dyDescent="0.45">
       <c r="S14">
         <v>20</v>
       </c>
@@ -81341,7 +81351,7 @@
         <v>8.0442270058708409E-2</v>
       </c>
     </row>
-    <row r="15" spans="14:20" x14ac:dyDescent="0.6">
+    <row r="15" spans="14:20" x14ac:dyDescent="0.45">
       <c r="S15">
         <v>25</v>
       </c>
@@ -81350,7 +81360,7 @@
         <v>0.10055283757338553</v>
       </c>
     </row>
-    <row r="16" spans="14:20" x14ac:dyDescent="0.6">
+    <row r="16" spans="14:20" x14ac:dyDescent="0.45">
       <c r="S16">
         <v>40</v>
       </c>
@@ -81359,7 +81369,7 @@
         <v>0.16088454011741682</v>
       </c>
     </row>
-    <row r="17" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="17" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S17">
         <v>50</v>
       </c>
@@ -81368,7 +81378,7 @@
         <v>0.20110567514677105</v>
       </c>
     </row>
-    <row r="18" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="18" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S18">
         <v>60</v>
       </c>
@@ -81377,7 +81387,7 @@
         <v>0.24132681017612523</v>
       </c>
     </row>
-    <row r="19" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="19" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S19">
         <v>70</v>
       </c>
@@ -81386,7 +81396,7 @@
         <v>0.28154794520547943</v>
       </c>
     </row>
-    <row r="20" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="20" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S20">
         <v>80</v>
       </c>
@@ -81395,7 +81405,7 @@
         <v>0.32176908023483364</v>
       </c>
     </row>
-    <row r="21" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="21" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S21">
         <v>90</v>
       </c>
@@ -81404,7 +81414,7 @@
         <v>0.3619902152641879</v>
       </c>
     </row>
-    <row r="22" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="22" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S22">
         <v>100</v>
       </c>
@@ -81413,7 +81423,7 @@
         <v>0.4022113502935421</v>
       </c>
     </row>
-    <row r="23" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="23" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S23">
         <v>110</v>
       </c>
@@ -81422,7 +81432,7 @@
         <v>0.44243248532289625</v>
       </c>
     </row>
-    <row r="24" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="24" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S24">
         <v>120</v>
       </c>
@@ -81431,7 +81441,7 @@
         <v>0.48265362035225046</v>
       </c>
     </row>
-    <row r="25" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="25" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S25">
         <v>130</v>
       </c>
@@ -81440,7 +81450,7 @@
         <v>0.52287475538160466</v>
       </c>
     </row>
-    <row r="26" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="26" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S26">
         <v>140</v>
       </c>
@@ -81449,7 +81459,7 @@
         <v>0.56309589041095887</v>
       </c>
     </row>
-    <row r="27" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="27" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S27">
         <v>150</v>
       </c>
@@ -81458,7 +81468,7 @@
         <v>0.60331702544031307</v>
       </c>
     </row>
-    <row r="28" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="28" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S28">
         <v>160</v>
       </c>
@@ -81467,7 +81477,7 @@
         <v>0.64353816046966728</v>
       </c>
     </row>
-    <row r="29" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="29" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S29">
         <v>170</v>
       </c>
@@ -81476,7 +81486,7 @@
         <v>0.68375929549902159</v>
       </c>
     </row>
-    <row r="30" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="30" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S30">
         <v>180</v>
       </c>
@@ -81485,7 +81495,7 @@
         <v>0.7239804305283758</v>
       </c>
     </row>
-    <row r="31" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="31" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S31">
         <v>190</v>
       </c>
@@ -81494,7 +81504,7 @@
         <v>0.76420156555773</v>
       </c>
     </row>
-    <row r="32" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="32" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S32">
         <v>200</v>
       </c>
@@ -81503,7 +81513,7 @@
         <v>0.80442270058708421</v>
       </c>
     </row>
-    <row r="33" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="33" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S33">
         <v>210</v>
       </c>
@@ -81512,7 +81522,7 @@
         <v>0.84464383561643841</v>
       </c>
     </row>
-    <row r="34" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="34" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S34">
         <v>220</v>
       </c>
@@ -81521,7 +81531,7 @@
         <v>0.8848649706457925</v>
       </c>
     </row>
-    <row r="35" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="35" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S35">
         <v>230</v>
       </c>
@@ -81530,7 +81540,7 @@
         <v>0.92508610567514671</v>
       </c>
     </row>
-    <row r="36" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="36" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S36">
         <v>240</v>
       </c>
@@ -81539,7 +81549,7 @@
         <v>0.96530724070450091</v>
       </c>
     </row>
-    <row r="37" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="37" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S37">
         <v>250</v>
       </c>
@@ -81548,7 +81558,7 @@
         <v>1.0055283757338551</v>
       </c>
     </row>
-    <row r="38" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="38" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S38">
         <v>256</v>
       </c>
@@ -81557,7 +81567,7 @@
         <v>1.0296610567514677</v>
       </c>
     </row>
-    <row r="39" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="39" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S39">
         <v>270</v>
       </c>
@@ -81566,7 +81576,7 @@
         <v>1.0859706457925635</v>
       </c>
     </row>
-    <row r="40" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="40" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S40">
         <v>280</v>
       </c>
@@ -81575,7 +81585,7 @@
         <v>1.1261917808219177</v>
       </c>
     </row>
-    <row r="41" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="41" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S41">
         <v>290</v>
       </c>
@@ -81584,7 +81594,7 @@
         <v>1.1664129158512719</v>
       </c>
     </row>
-    <row r="42" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="42" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S42">
         <v>300</v>
       </c>
@@ -81593,7 +81603,7 @@
         <v>1.2066340508806261</v>
       </c>
     </row>
-    <row r="43" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="43" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S43">
         <v>310</v>
       </c>
@@ -81602,7 +81612,7 @@
         <v>1.2468551859099803</v>
       </c>
     </row>
-    <row r="44" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="44" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S44">
         <v>320</v>
       </c>
@@ -81611,7 +81621,7 @@
         <v>1.2870763209393346</v>
       </c>
     </row>
-    <row r="45" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="45" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S45">
         <v>330</v>
       </c>
@@ -81620,7 +81630,7 @@
         <v>1.327297455968689</v>
       </c>
     </row>
-    <row r="46" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="46" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S46">
         <v>340</v>
       </c>
@@ -81629,7 +81639,7 @@
         <v>1.3675185909980432</v>
       </c>
     </row>
-    <row r="47" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="47" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S47">
         <v>350</v>
       </c>
@@ -81638,7 +81648,7 @@
         <v>1.4077397260273974</v>
       </c>
     </row>
-    <row r="48" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="48" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S48">
         <v>360</v>
       </c>
@@ -81647,7 +81657,7 @@
         <v>1.4479608610567516</v>
       </c>
     </row>
-    <row r="49" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="49" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S49">
         <v>370</v>
       </c>
@@ -81656,7 +81666,7 @@
         <v>1.4881819960861058</v>
       </c>
     </row>
-    <row r="50" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="50" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S50">
         <v>380</v>
       </c>
@@ -81665,7 +81675,7 @@
         <v>1.52840313111546</v>
       </c>
     </row>
-    <row r="51" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="51" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S51">
         <v>390</v>
       </c>
@@ -81674,7 +81684,7 @@
         <v>1.5686242661448142</v>
       </c>
     </row>
-    <row r="52" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="52" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S52">
         <v>400</v>
       </c>
@@ -81683,7 +81693,7 @@
         <v>1.6088454011741684</v>
       </c>
     </row>
-    <row r="53" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="53" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S53">
         <v>410</v>
       </c>
@@ -81692,7 +81702,7 @@
         <v>1.6490665362035226</v>
       </c>
     </row>
-    <row r="54" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="54" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S54">
         <v>420</v>
       </c>
@@ -81701,7 +81711,7 @@
         <v>1.6892876712328768</v>
       </c>
     </row>
-    <row r="55" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="55" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S55">
         <v>430</v>
       </c>
@@ -81710,7 +81720,7 @@
         <v>1.7295088062622308</v>
       </c>
     </row>
-    <row r="56" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="56" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S56">
         <v>440</v>
       </c>
@@ -81719,7 +81729,7 @@
         <v>1.769729941291585</v>
       </c>
     </row>
-    <row r="57" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="57" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S57">
         <v>450</v>
       </c>
@@ -81728,7 +81738,7 @@
         <v>1.8099510763209392</v>
       </c>
     </row>
-    <row r="58" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="58" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S58">
         <v>460</v>
       </c>
@@ -81737,7 +81747,7 @@
         <v>1.8501722113502934</v>
       </c>
     </row>
-    <row r="59" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="59" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S59">
         <v>470</v>
       </c>
@@ -81746,7 +81756,7 @@
         <v>1.8903933463796476</v>
       </c>
     </row>
-    <row r="60" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="60" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S60">
         <v>480</v>
       </c>
@@ -81755,7 +81765,7 @@
         <v>1.9306144814090018</v>
       </c>
     </row>
-    <row r="61" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="61" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S61">
         <v>490</v>
       </c>
@@ -81764,7 +81774,7 @@
         <v>1.970835616438356</v>
       </c>
     </row>
-    <row r="62" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="62" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S62">
         <v>500</v>
       </c>
@@ -81773,7 +81783,7 @@
         <v>2.0110567514677102</v>
       </c>
     </row>
-    <row r="63" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="63" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S63">
         <v>510</v>
       </c>
@@ -81782,7 +81792,7 @@
         <v>2.0512778864970644</v>
       </c>
     </row>
-    <row r="64" spans="19:20" x14ac:dyDescent="0.6">
+    <row r="64" spans="19:20" x14ac:dyDescent="0.45">
       <c r="S64">
         <v>511</v>
       </c>
@@ -81802,19 +81812,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB93098E-C600-4E1F-87B3-6E0B6E069199}">
   <dimension ref="B2:H43"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.625" customWidth="1"/>
-    <col min="2" max="2" width="8.1875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.6875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="1.8125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.9375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.58203125" customWidth="1"/>
+    <col min="2" max="2" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="1.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.9140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="12.3125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
         <v>43</v>
       </c>
@@ -81825,7 +81835,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
         <v>42</v>
@@ -81842,7 +81852,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
@@ -81863,7 +81873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
@@ -81884,7 +81894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
@@ -81905,7 +81915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
@@ -81923,7 +81933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
@@ -81944,7 +81954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
@@ -81965,7 +81975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
@@ -81983,7 +81993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
@@ -82004,7 +82014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
@@ -82025,7 +82035,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
@@ -82046,7 +82056,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
@@ -82067,7 +82077,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
@@ -82088,7 +82098,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
@@ -82109,13 +82119,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.45">
       <c r="E17" s="1">
         <f>SUM(E4:E16)</f>
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B19" s="2" t="s">
         <v>44</v>
       </c>
@@ -82126,7 +82136,7 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B20" s="3"/>
       <c r="C20" s="3" t="s">
         <v>42</v>
@@ -82143,7 +82153,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
@@ -82164,7 +82174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
@@ -82185,7 +82195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
@@ -82206,7 +82216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B24" s="1" t="s">
         <v>6</v>
       </c>
@@ -82227,7 +82237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
@@ -82245,7 +82255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
@@ -82266,7 +82276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B27" s="1" t="s">
         <v>6</v>
       </c>
@@ -82287,7 +82297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B28" s="1" t="s">
         <v>6</v>
       </c>
@@ -82308,7 +82318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
@@ -82329,7 +82339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
@@ -82350,7 +82360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B31" s="1" t="s">
         <v>6</v>
       </c>
@@ -82368,7 +82378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B32" s="1" t="s">
         <v>6</v>
       </c>
@@ -82389,7 +82399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
@@ -82410,7 +82420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B34" s="1" t="s">
         <v>6</v>
       </c>
@@ -82431,7 +82441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B35" s="1" t="s">
         <v>6</v>
       </c>
@@ -82452,7 +82462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B36" s="1" t="s">
         <v>6</v>
       </c>
@@ -82473,7 +82483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
@@ -82494,7 +82504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B38" s="1" t="s">
         <v>6</v>
       </c>
@@ -82515,7 +82525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B39" s="1" t="s">
         <v>6</v>
       </c>
@@ -82536,7 +82546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B40" s="1" t="s">
         <v>6</v>
       </c>
@@ -82557,7 +82567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B41" s="1" t="s">
         <v>6</v>
       </c>
@@ -82578,7 +82588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B42" s="1" t="s">
         <v>6</v>
       </c>
@@ -82599,7 +82609,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.45">
       <c r="E43" s="1">
         <f>SUM(E21:E42)</f>
         <v>48</v>
